--- a/src/Tests/Templates/CompanyDirectives.xlsx
+++ b/src/Tests/Templates/CompanyDirectives.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
-  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <x:workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nevolin_DA\Desktop\rx-util-importdata-net-core\src\Tests\bin\Debug\net6.0\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Utilites\rx-util-importdata-net-core\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <x:bookViews>
-    <x:workbookView xWindow="480" yWindow="105" windowWidth="17100" windowHeight="9855"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Распоряжения" sheetId="2" r:id="rId1"/>
-  </x:sheets>
-  <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Распоряжения!$A$1:$Q$1</x:definedName>
-  </x:definedNames>
-  <x:calcPr calcId="152511" refMode="R1C1"/>
-</x:workbook>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="105" windowWidth="17100" windowHeight="9855"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Распоряжения" sheetId="2" r:id="rId1"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Распоряжения!$A$1:$Q$1</definedName>
+  </definedNames>
+  <calcPr calcId="152511" refMode="R1C1"/>
+</workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -174,153 +174,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
-  <x:si>
-    <x:t>Содержание</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Примечание</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Файл</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Состояние</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Итог</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Подробности</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Рег. №</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Наша организация</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Подразделение</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Исполнитель</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Подготовил</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Подписал</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Журнал регистрации</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Распоряжение</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Отдел снабжения</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Действующий</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Прим</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Зарегистрирован</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Регистрация</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1559595546</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Не загружен</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ТехноСистемы ЗАО</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Templates\TestDocs\testDoc.txt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иванов Иван Иванович</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Законов Сергей Юрьевич</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Добрынин Никита</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Приложение не может быть импортировано. Не найден журнал регистрации по ИД "18"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Загружен</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>1200195955</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.05.2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1359448219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>175856062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1340512682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1993667614</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Не удается создать тело документа. Ошибка: "Object reference not set to an instance of an object."; Object reference not set to an instance of an object.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Загружен частично</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Найдено несколько записей типа сущности "Сотрудник" с именем "Иванов Иван Иванович". Проверьте, что выбрана верная запись.
-Найдено несколько записей типа сущности "Сотрудник" с именем "Добрынин Никита". Проверьте, что выбрана верная запись.</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>Содержание</t>
+  </si>
+  <si>
+    <t>Примечание</t>
+  </si>
+  <si>
+    <t>Файл</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Состояние</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>Подробности</t>
+  </si>
+  <si>
+    <t>Рег. №</t>
+  </si>
+  <si>
+    <t>Наша организация</t>
+  </si>
+  <si>
+    <t>Подразделение</t>
+  </si>
+  <si>
+    <t>Исполнитель</t>
+  </si>
+  <si>
+    <t>Подготовил</t>
+  </si>
+  <si>
+    <t>Подписал</t>
+  </si>
+  <si>
+    <t>Журнал регистрации</t>
+  </si>
+  <si>
+    <t>Распоряжение</t>
+  </si>
+  <si>
+    <t>Отдел снабжения</t>
+  </si>
+  <si>
+    <t>Действующий</t>
+  </si>
+  <si>
+    <t>Прим</t>
+  </si>
+  <si>
+    <t>Зарегистрирован</t>
+  </si>
+  <si>
+    <t>Регистрация</t>
+  </si>
+  <si>
+    <t>ТехноСистемы ЗАО</t>
+  </si>
+  <si>
+    <t>Templates\TestDocs\testDoc.txt</t>
+  </si>
+  <si>
+    <t>Иванов Иван Иванович</t>
+  </si>
+  <si>
+    <t>Законов Сергей Юрьевич</t>
+  </si>
+  <si>
+    <t>Добрынин Никита</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -899,157 +832,151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:dimension ref="A1:T4"/>
-  <x:sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <x:cols>
-    <x:col min="1" max="14" width="23.42578125" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <x:c r="A1" s="14" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B1" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="14" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D1" s="14" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1" s="14" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="16" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G1" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I1" s="17" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J1" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K1" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L1" s="12" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="N1" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="O1" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P1" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q1" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <x:c r="A2" s="19" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B2" s="20">
-        <x:v>44239</x:v>
-      </x:c>
-      <x:c r="C2" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="21" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2" s="27" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F2" s="21" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="28" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H2" s="22" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I2" s="23" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J2" s="24" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K2" s="25" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L2" s="24" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M2" s="24">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="N2" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="O2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="P2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Q2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="R2"/>
-      <x:c r="S2"/>
-      <x:c r="T2"/>
-    </x:row>
-    <x:row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="2"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-      <x:c r="F3" s="3"/>
-      <x:c r="G3" s="4"/>
-      <x:c r="H3" s="5"/>
-      <x:c r="I3" s="6"/>
-      <x:c r="J3" s="7"/>
-      <x:c r="K3" s="8"/>
-      <x:c r="L3" s="7"/>
-      <x:c r="M3" s="7"/>
-      <x:c r="N3" s="26"/>
-    </x:row>
-    <x:row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <x:c r="A4" s="9"/>
-      <x:c r="B4" s="2"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="7"/>
-      <x:c r="K4" s="7"/>
-      <x:c r="L4" s="7"/>
-      <x:c r="M4" s="7"/>
-      <x:c r="N4" s="26"/>
-    </x:row>
-  </x:sheetData>
-  <x:autoFilter ref="A1:Q1"/>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing r:id="rId1"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="14" width="23.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="20">
+        <v>44239</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="24">
+        <v>21</v>
+      </c>
+      <c r="N2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="26"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="9"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="26"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>